--- a/artfynd/A 1470-2023 artfynd.xlsx
+++ b/artfynd/A 1470-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1470-2023 artfynd.xlsx
+++ b/artfynd/A 1470-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110904986</v>
+        <v>110905348</v>
       </c>
       <c r="B2" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460261.7317011741</v>
+        <v>460202</v>
       </c>
       <c r="R2" t="n">
-        <v>7190635.96465066</v>
+        <v>7190575</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110905496</v>
+        <v>110905088</v>
       </c>
       <c r="B3" t="n">
-        <v>56753</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460150</v>
+        <v>460284</v>
       </c>
       <c r="R3" t="n">
-        <v>7190539</v>
+        <v>7190643</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -865,11 +845,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,56 +871,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110903913</v>
+        <v>110903363</v>
       </c>
       <c r="B4" t="n">
-        <v>56753</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Messätern, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460015</v>
+        <v>460026</v>
       </c>
       <c r="R4" t="n">
-        <v>7190579</v>
+        <v>7190635</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,11 +943,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,19 +969,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110904910</v>
+        <v>110904271</v>
       </c>
       <c r="B5" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1050,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460247.6629838182</v>
+        <v>460083</v>
       </c>
       <c r="R5" t="n">
-        <v>7190635.725145563</v>
+        <v>7190631</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1083,19 +1038,9 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,37 +1067,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110904403</v>
+        <v>110904598</v>
       </c>
       <c r="B6" t="n">
-        <v>103273</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460111.885949833</v>
+        <v>460165</v>
       </c>
       <c r="R6" t="n">
-        <v>7190617.942853552</v>
+        <v>7190592</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1196,19 +1136,9 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,37 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110904058</v>
+        <v>110904910</v>
       </c>
       <c r="B7" t="n">
-        <v>96265</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1276,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460014.6099991123</v>
+        <v>460247</v>
       </c>
       <c r="R7" t="n">
-        <v>7190578.793487678</v>
+        <v>7190635</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1309,19 +1234,9 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,19 +1263,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110904598</v>
+        <v>110905127</v>
       </c>
       <c r="B8" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1389,10 +1299,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460165.2429280909</v>
+        <v>460291</v>
       </c>
       <c r="R8" t="n">
-        <v>7190591.691704352</v>
+        <v>7190636</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,19 +1332,9 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,37 +1361,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110905583</v>
+        <v>110905053</v>
       </c>
       <c r="B9" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1502,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460102.0847949881</v>
+        <v>460239</v>
       </c>
       <c r="R9" t="n">
-        <v>7190521.860340065</v>
+        <v>7190659</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1535,19 +1430,14 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,15 +1464,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110903852</v>
+        <v>110903242</v>
       </c>
       <c r="B10" t="n">
-        <v>56753</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1615,10 +1500,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460033</v>
+        <v>460005</v>
       </c>
       <c r="R10" t="n">
-        <v>7190577</v>
+        <v>7190708</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1682,15 +1567,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110905348</v>
+        <v>110903852</v>
       </c>
       <c r="B11" t="n">
-        <v>85715</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,21 +1578,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460201.2409214427</v>
+        <v>460033</v>
       </c>
       <c r="R11" t="n">
-        <v>7190574.185698131</v>
+        <v>7190577</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1756,19 +1636,14 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,15 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110904271</v>
+        <v>110903913</v>
       </c>
       <c r="B12" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,35 +1681,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Messätern, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460082.6452194319</v>
+        <v>460014</v>
       </c>
       <c r="R12" t="n">
-        <v>7190630.677054459</v>
+        <v>7190579</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1869,19 +1744,14 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1908,15 +1778,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110905560</v>
+        <v>110904229</v>
       </c>
       <c r="B13" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1924,21 +1789,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1949,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460110.4385859943</v>
+        <v>460056</v>
       </c>
       <c r="R13" t="n">
-        <v>7190508.977536551</v>
+        <v>7190605</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1982,19 +1847,14 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2021,15 +1881,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110905127</v>
+        <v>110904525</v>
       </c>
       <c r="B14" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2037,21 +1892,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2062,10 +1917,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460291.5737417982</v>
+        <v>460159</v>
       </c>
       <c r="R14" t="n">
-        <v>7190636.42131759</v>
+        <v>7190602</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2095,19 +1950,14 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2134,15 +1984,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>110902774</v>
+        <v>110905496</v>
       </c>
       <c r="B15" t="n">
-        <v>56543</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2150,40 +1995,35 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Messätern, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459859.6059127586</v>
+        <v>460150</v>
       </c>
       <c r="R15" t="n">
-        <v>7190876.721864637</v>
+        <v>7190538</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2213,19 +2053,14 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2252,15 +2087,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>110904525</v>
+        <v>110902774</v>
       </c>
       <c r="B16" t="n">
-        <v>56753</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2268,35 +2098,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Messätern, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460159</v>
+        <v>459859</v>
       </c>
       <c r="R16" t="n">
-        <v>7190602</v>
+        <v>7190877</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2329,11 +2164,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2360,37 +2190,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>110905378</v>
+        <v>110904058</v>
       </c>
       <c r="B17" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2401,10 +2226,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460214.8700896954</v>
+        <v>460014</v>
       </c>
       <c r="R17" t="n">
-        <v>7190541.22456655</v>
+        <v>7190579</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2434,19 +2259,9 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2473,37 +2288,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>110904229</v>
+        <v>110903280</v>
       </c>
       <c r="B18" t="n">
-        <v>56753</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2514,10 +2324,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460056</v>
+        <v>460017</v>
       </c>
       <c r="R18" t="n">
-        <v>7190605</v>
+        <v>7190673</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2550,11 +2360,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2581,37 +2386,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>110905460</v>
+        <v>110904403</v>
       </c>
       <c r="B19" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>221725</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2622,10 +2422,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460187.8691808072</v>
+        <v>460112</v>
       </c>
       <c r="R19" t="n">
-        <v>7190530.087839582</v>
+        <v>7190618</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2655,19 +2455,9 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,571 +2481,6 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>110903280</v>
-      </c>
-      <c r="B20" t="n">
-        <v>96674</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>219880</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Kransrams</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Polygonatum verticillatum</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Messätern, Jmt</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>460017.1409385363</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7190672.842240245</v>
-      </c>
-      <c r="S20" t="n">
-        <v>25</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Frostviken</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>110905088</v>
-      </c>
-      <c r="B21" t="n">
-        <v>89401</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Messätern, Jmt</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>460284.4191924931</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7190643.327280905</v>
-      </c>
-      <c r="S21" t="n">
-        <v>25</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Frostviken</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>110905053</v>
-      </c>
-      <c r="B22" t="n">
-        <v>78605</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Messätern, Jmt</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>460239.4385912765</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7190658.396579986</v>
-      </c>
-      <c r="S22" t="n">
-        <v>25</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Frostviken</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På rönn</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>110903242</v>
-      </c>
-      <c r="B23" t="n">
-        <v>56753</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Messätern, Jmt</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>460005</v>
-      </c>
-      <c r="R23" t="n">
-        <v>7190707</v>
-      </c>
-      <c r="S23" t="n">
-        <v>25</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Frostviken</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>110903363</v>
-      </c>
-      <c r="B24" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Messätern, Jmt</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>460026.8642637678</v>
-      </c>
-      <c r="R24" t="n">
-        <v>7190634.824740495</v>
-      </c>
-      <c r="S24" t="n">
-        <v>25</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Frostviken</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1470-2023 artfynd.xlsx
+++ b/artfynd/A 1470-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110905348</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110905088</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110903363</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110904271</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110904598</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1260,6 +1290,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110904910</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1358,6 +1393,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110905127</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1461,6 +1501,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110905053</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1564,6 +1609,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110903242</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1667,6 +1717,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110903852</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1775,6 +1830,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110903913</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1878,6 +1938,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110904229</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1981,6 +2046,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110904525</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2084,6 +2154,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110905496</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110902774</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2285,6 +2365,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110904058</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2383,6 +2468,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110903280</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2481,8 +2571,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110904403</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>